--- a/output/pdf_financials_xlsx/SPI.xlsx
+++ b/output/pdf_financials_xlsx/SPI.xlsx
@@ -7460,52 +7460,52 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-19.51183</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-8.944589000000001</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-1.526456</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-1.339751</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-9.816908</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.13858</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-3.653539</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.670614</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.5960220000000001</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.179833</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.07330399999999999</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.111512</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.14775</v>
+        <v>0.051769</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.078191</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>5</v>
+        <v>4.962228</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.043411</v>
       </c>
     </row>
     <row r="119">
@@ -26101,7 +26101,11 @@
           <t>Exploration and evaluation expenditures (Note 6)</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -31990,7 +31994,11 @@
           <t>Exploration and evaluation expenditures (note 6)</t>
         </is>
       </c>
-      <c r="D239" t="inlineStr"/>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E239" t="inlineStr">
         <is>
           <t>-</t>
@@ -33192,7 +33200,11 @@
           <t>Exploration and evaluation expense (note 6)</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -33962,7 +33974,11 @@
           <t>Exploration and evaluation expenditures (note 6)</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -37255,7 +37271,11 @@
           <t>Exploration and evaluation expenditures (note 6)</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E292" t="inlineStr">
         <is>
           <t>-</t>
@@ -38748,7 +38768,11 @@
           <t>Exploration and evaluation expenditures (note 6)</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SPI.xlsx
+++ b/output/pdf_financials_xlsx/SPI.xlsx
@@ -2447,22 +2447,22 @@
         <v>0.639696</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.324768</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.282795</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.7702830000000001</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>1.176782</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>5.608224</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>4.08968</v>
       </c>
     </row>
     <row r="35">
@@ -2563,22 +2563,22 @@
         <v>0.639696</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.324768</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.282795</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.7702830000000001</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>1.176782</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>5.608224</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>4.08968</v>
       </c>
     </row>
     <row r="37">
@@ -3259,22 +3259,22 @@
         <v>0.035676</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.356336</v>
+        <v>0.031568</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.331688</v>
+        <v>0.048893</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.799173</v>
+        <v>0.02889</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.186412</v>
+        <v>0.00963</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>5.655967</v>
+        <v>0.047743</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>4.169084</v>
+        <v>0.079404</v>
       </c>
     </row>
     <row r="49">
@@ -7856,10 +7856,10 @@
         <v>0</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="125">
@@ -7914,10 +7914,10 @@
         <v>0</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="R125" s="3" t="n">
-        <v>0</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="126">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -25903,7 +25903,11 @@
           <t>Lease payments (Note 9)</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -55620,7 +55624,11 @@
           <t>General and administrative, net</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E477" t="inlineStr">
         <is>
           <t>-</t>
@@ -56481,7 +56489,11 @@
           <t>General and administrative, net (note 22)</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E486" t="inlineStr">
         <is>
           <t>-</t>
@@ -57166,7 +57178,11 @@
           <t>General and administrative, net (note 23)</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E493" t="inlineStr">
         <is>
           <t>-</t>
@@ -57667,7 +57683,11 @@
           <t>General and administrative, net (note 17)</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SPI.xlsx
+++ b/output/pdf_financials_xlsx/SPI.xlsx
@@ -2765,28 +2765,28 @@
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>0.03378</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>0.022653</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.010967</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.007696</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.008340999999999999</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>0.01477</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.009032</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.006338</v>
       </c>
       <c r="K40" s="3" t="n">
         <v>0</v>
@@ -2823,28 +2823,28 @@
         <v>0.203995</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.203995</v>
+        <v>0.237775</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.074255</v>
+        <v>0.09690799999999999</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.282395</v>
+        <v>0.293362</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.238256</v>
+        <v>0.245952</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.121958</v>
+        <v>0.130299</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.038019</v>
+        <v>0.052789</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.107287</v>
+        <v>0.116319</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.039303</v>
+        <v>0.045641</v>
       </c>
       <c r="K41" s="3" t="n">
         <v>0.014668</v>
@@ -3229,28 +3229,28 @@
         <v>0.05129</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.05129</v>
+        <v>0.01751</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.488935</v>
+        <v>0.466282</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.41595</v>
+        <v>0.404983</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.397395</v>
+        <v>0.389699</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.266718</v>
+        <v>0.258377</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.170444</v>
+        <v>0.155674</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.12784</v>
+        <v>0.118808</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.120702</v>
+        <v>0.114364</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.062582</v>
@@ -6993,10 +6993,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.023651</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.039465</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -7020,16 +7020,16 @@
         <v>0</v>
       </c>
       <c r="K110" s="3" t="n">
-        <v>0</v>
+        <v>0.048072</v>
       </c>
       <c r="L110" s="3" t="n">
-        <v>0</v>
+        <v>0.053921</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0</v>
+        <v>0.009629</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0</v>
+        <v>0.032605</v>
       </c>
       <c r="O110" s="3" t="n">
         <v>0</v>
@@ -27972,7 +27972,11 @@
           <t>Accretion (Notes 10 and 13)</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -29984,7 +29988,11 @@
           <t>Accretion (Notes 9 and 12)</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -30586,7 +30594,11 @@
           <t>Common shares issued for cash (Note 13)</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -31695,7 +31707,11 @@
           <t>Common shares issued for cash (note 11)</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -33679,7 +33695,11 @@
           <t>Common shares issued for cash (note 13)</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -36869,7 +36889,11 @@
           <t>Common shares issued for cash (note 12)</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -38273,7 +38297,11 @@
           <t>Common shares issued for cash (note 12)</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
           <t>-</t>
@@ -39556,7 +39584,11 @@
           <t>Common shares issued for cash (note 13)</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E315" t="inlineStr">
         <is>
           <t>-</t>
@@ -44893,7 +44925,11 @@
           <t>Accretion (note 4)</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E368" s="5" t="n">
         <v>0.023651</v>
       </c>
@@ -45299,7 +45335,11 @@
           <t>Common shares issued for cash (note 5)</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E372" s="5" t="n">
         <v>0.5589</v>
       </c>
